--- a/sources/table_normalization/xlsx/food-table09.xlsx
+++ b/sources/table_normalization/xlsx/food-table09.xlsx
@@ -255,7 +255,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -401,10 +401,10 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -428,22 +428,22 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -942,77 +942,77 @@
       <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24" t="s">
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="24"/>
-      <c r="J1" s="19" t="s">
+      <c r="I1" s="22"/>
+      <c r="J1" s="20" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="21" t="s">
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21" t="s">
+      <c r="E2" s="23"/>
+      <c r="F2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21" t="s">
+      <c r="G2" s="23"/>
+      <c r="H2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="21"/>
-      <c r="J2" s="22"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="21"/>
     </row>
     <row r="3" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21" t="s">
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21" t="s">
+      <c r="G3" s="23"/>
+      <c r="H3" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="21"/>
-      <c r="J3" s="22"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="21"/>
     </row>
     <row r="4" spans="1:10" ht="20.149999999999999" customHeight="1">
-      <c r="A4" s="20"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="23" t="s">
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="22"/>
+      <c r="J4" s="21"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
